--- a/research/traditional_assets/database/data/bermuda/bermuda_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0635</v>
+        <v>0.0282</v>
       </c>
       <c r="E2">
-        <v>0.0399</v>
+        <v>0.0247</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.01121596123237953</v>
+        <v>-0.006578210361886953</v>
       </c>
       <c r="J2">
-        <v>-0.00876611531683749</v>
+        <v>-0.005050993827027524</v>
       </c>
       <c r="K2">
-        <v>507.6</v>
+        <v>525.5</v>
       </c>
       <c r="L2">
-        <v>0.1655037495924356</v>
+        <v>0.1720581494335669</v>
       </c>
       <c r="M2">
-        <v>483.2</v>
+        <v>919.4000000000001</v>
       </c>
       <c r="N2">
-        <v>0.1076552891899118</v>
+        <v>0.3086581394568101</v>
       </c>
       <c r="O2">
-        <v>0.9519306540583136</v>
+        <v>1.749571836346337</v>
       </c>
       <c r="P2">
-        <v>197</v>
+        <v>187.3</v>
       </c>
       <c r="Q2">
-        <v>0.04389091881294003</v>
+        <v>0.0628797797696982</v>
       </c>
       <c r="R2">
-        <v>0.3881008668242711</v>
+        <v>0.3564224548049477</v>
       </c>
       <c r="S2">
-        <v>286.2</v>
+        <v>732.1000000000001</v>
       </c>
       <c r="T2">
-        <v>0.5923013245033113</v>
+        <v>0.796280182727866</v>
       </c>
       <c r="U2">
-        <v>1184.8</v>
+        <v>1000.1</v>
       </c>
       <c r="V2">
-        <v>0.2639693431957936</v>
+        <v>0.3357504951824622</v>
       </c>
       <c r="W2">
-        <v>0.7316229460939753</v>
+        <v>0.5986557302346777</v>
       </c>
       <c r="X2">
-        <v>0.05022553774105876</v>
+        <v>0.1007241411887352</v>
       </c>
       <c r="Y2">
-        <v>0.6813974083529165</v>
+        <v>0.4979315890459424</v>
       </c>
       <c r="Z2">
-        <v>1.694665422365887</v>
+        <v>1.631468419752576</v>
       </c>
       <c r="AA2">
-        <v>-0.01485563251591648</v>
+        <v>-0.008240536917160613</v>
       </c>
       <c r="AB2">
-        <v>0.0428622848729161</v>
+        <v>0.08106367527907257</v>
       </c>
       <c r="AC2">
-        <v>-0.05771791738883258</v>
+        <v>-0.08930421219623319</v>
       </c>
       <c r="AD2">
-        <v>2055.3</v>
+        <v>1998.2</v>
       </c>
       <c r="AE2">
-        <v>631.4967654985401</v>
+        <v>503.4558504363756</v>
       </c>
       <c r="AF2">
-        <v>2686.79676549854</v>
+        <v>2501.655850436376</v>
       </c>
       <c r="AG2">
-        <v>1501.996765498541</v>
+        <v>1501.555850436376</v>
       </c>
       <c r="AH2">
-        <v>0.3744561791556471</v>
+        <v>0.4564769001701195</v>
       </c>
       <c r="AI2">
-        <v>0.6337537009967712</v>
+        <v>0.6657844962159285</v>
       </c>
       <c r="AJ2">
-        <v>0.2507341039827667</v>
+        <v>0.3351495763997774</v>
       </c>
       <c r="AK2">
-        <v>0.4917007745131808</v>
+        <v>0.5445636805270315</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>22.36452665941241</v>
+        <v>24.79156327543425</v>
       </c>
       <c r="AP2">
-        <v>16.34381681717672</v>
+        <v>18.62972519151831</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0635</v>
+        <v>0.0282</v>
       </c>
       <c r="E3">
-        <v>0.0399</v>
+        <v>0.0247</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,91 +728,91 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.01121596123237953</v>
+        <v>-0.006578210361886953</v>
       </c>
       <c r="J3">
-        <v>-0.00876611531683749</v>
+        <v>-0.005050993827027524</v>
       </c>
       <c r="K3">
-        <v>507.6</v>
+        <v>525.5</v>
       </c>
       <c r="L3">
-        <v>0.1655037495924356</v>
+        <v>0.1720581494335669</v>
       </c>
       <c r="M3">
-        <v>483.2</v>
+        <v>919.4000000000001</v>
       </c>
       <c r="N3">
-        <v>0.1076552891899118</v>
+        <v>0.3086581394568101</v>
       </c>
       <c r="O3">
-        <v>0.9519306540583136</v>
+        <v>1.749571836346337</v>
       </c>
       <c r="P3">
-        <v>197</v>
+        <v>187.3</v>
       </c>
       <c r="Q3">
-        <v>0.04389091881294003</v>
+        <v>0.0628797797696982</v>
       </c>
       <c r="R3">
-        <v>0.3881008668242711</v>
+        <v>0.3564224548049477</v>
       </c>
       <c r="S3">
-        <v>286.2</v>
+        <v>732.1000000000001</v>
       </c>
       <c r="T3">
-        <v>0.5923013245033113</v>
+        <v>0.796280182727866</v>
       </c>
       <c r="U3">
-        <v>1184.8</v>
+        <v>1000.1</v>
       </c>
       <c r="V3">
-        <v>0.2639693431957936</v>
+        <v>0.3357504951824622</v>
       </c>
       <c r="W3">
-        <v>0.7316229460939753</v>
+        <v>0.5986557302346777</v>
       </c>
       <c r="X3">
-        <v>0.05022553774105876</v>
+        <v>0.1007241411887352</v>
       </c>
       <c r="Y3">
-        <v>0.6813974083529165</v>
+        <v>0.4979315890459424</v>
       </c>
       <c r="Z3">
-        <v>1.694665422365887</v>
+        <v>1.631468419752576</v>
       </c>
       <c r="AA3">
-        <v>-0.01485563251591648</v>
+        <v>-0.008240536917160613</v>
       </c>
       <c r="AB3">
-        <v>0.0428622848729161</v>
+        <v>0.08106367527907257</v>
       </c>
       <c r="AC3">
-        <v>-0.05771791738883258</v>
+        <v>-0.08930421219623319</v>
       </c>
       <c r="AD3">
-        <v>2055.3</v>
+        <v>1998.2</v>
       </c>
       <c r="AE3">
-        <v>631.4967654985401</v>
+        <v>503.4558504363756</v>
       </c>
       <c r="AF3">
-        <v>2686.79676549854</v>
+        <v>2501.655850436376</v>
       </c>
       <c r="AG3">
-        <v>1501.996765498541</v>
+        <v>1501.555850436376</v>
       </c>
       <c r="AH3">
-        <v>0.3744561791556471</v>
+        <v>0.4564769001701195</v>
       </c>
       <c r="AI3">
-        <v>0.6337537009967712</v>
+        <v>0.6657844962159285</v>
       </c>
       <c r="AJ3">
-        <v>0.2507341039827667</v>
+        <v>0.3351495763997774</v>
       </c>
       <c r="AK3">
-        <v>0.4917007745131808</v>
+        <v>0.5445636805270315</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>22.36452665941241</v>
+        <v>24.79156327543425</v>
       </c>
       <c r="AP3">
-        <v>16.34381681717672</v>
+        <v>18.62972519151831</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_brokerage_investment_banking.xlsx
@@ -588,10 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0282</v>
-      </c>
-      <c r="E2">
-        <v>0.0247</v>
+        <v>-0.028</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +597,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.006578210361886953</v>
+        <v>-0.006160473431558275</v>
       </c>
       <c r="J2">
-        <v>-0.005050993827027524</v>
+        <v>-0.006160473431558275</v>
       </c>
       <c r="K2">
-        <v>525.5</v>
+        <v>-96.7</v>
       </c>
       <c r="L2">
-        <v>0.1720581494335669</v>
+        <v>-0.03977132516245784</v>
       </c>
       <c r="M2">
-        <v>919.4000000000001</v>
+        <v>353.9</v>
       </c>
       <c r="N2">
-        <v>0.3086581394568101</v>
+        <v>0.1163379355687048</v>
       </c>
       <c r="O2">
-        <v>1.749571836346337</v>
+        <v>-3.659772492244053</v>
       </c>
       <c r="P2">
-        <v>187.3</v>
+        <v>172.3</v>
       </c>
       <c r="Q2">
-        <v>0.0628797797696982</v>
+        <v>0.05664036817882972</v>
       </c>
       <c r="R2">
-        <v>0.3564224548049477</v>
+        <v>-1.781799379524302</v>
       </c>
       <c r="S2">
-        <v>732.1000000000001</v>
+        <v>181.6</v>
       </c>
       <c r="T2">
-        <v>0.796280182727866</v>
+        <v>0.5131393048883864</v>
       </c>
       <c r="U2">
-        <v>1000.1</v>
+        <v>653.4</v>
       </c>
       <c r="V2">
-        <v>0.3357504951824622</v>
+        <v>0.214792899408284</v>
       </c>
       <c r="W2">
-        <v>0.5986557302346777</v>
+        <v>-0.1724937566892615</v>
       </c>
       <c r="X2">
-        <v>0.1007241411887352</v>
+        <v>0.07998372902819928</v>
       </c>
       <c r="Y2">
-        <v>0.4979315890459424</v>
+        <v>-0.2524774857174608</v>
       </c>
       <c r="Z2">
-        <v>1.631468419752576</v>
+        <v>1.471530886588896</v>
       </c>
       <c r="AA2">
-        <v>-0.008240536917160613</v>
+        <v>-0.009065326930548285</v>
       </c>
       <c r="AB2">
-        <v>0.08106367527907257</v>
+        <v>0.06837693492362432</v>
       </c>
       <c r="AC2">
-        <v>-0.08930421219623319</v>
+        <v>-0.07744226185417261</v>
       </c>
       <c r="AD2">
-        <v>1998.2</v>
+        <v>2032.1</v>
       </c>
       <c r="AE2">
-        <v>503.4558504363756</v>
+        <v>469.392875507454</v>
       </c>
       <c r="AF2">
-        <v>2501.655850436376</v>
+        <v>2501.492875507454</v>
       </c>
       <c r="AG2">
-        <v>1501.555850436376</v>
+        <v>1848.092875507454</v>
       </c>
       <c r="AH2">
-        <v>0.4564769001701195</v>
+        <v>0.4512485055333396</v>
       </c>
       <c r="AI2">
-        <v>0.6657844962159285</v>
+        <v>0.833055418477612</v>
       </c>
       <c r="AJ2">
-        <v>0.3351495763997774</v>
+        <v>0.3779259254489464</v>
       </c>
       <c r="AK2">
-        <v>0.5445636805270315</v>
+        <v>0.7866257256391302</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +690,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>24.79156327543425</v>
+        <v>25.7553865652725</v>
       </c>
       <c r="AP2">
-        <v>18.62972519151831</v>
+        <v>23.4232303613112</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +713,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0282</v>
-      </c>
-      <c r="E3">
-        <v>0.0247</v>
+        <v>-0.028</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,91 +722,91 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.006578210361886953</v>
+        <v>-0.006160473431558275</v>
       </c>
       <c r="J3">
-        <v>-0.005050993827027524</v>
+        <v>-0.006160473431558275</v>
       </c>
       <c r="K3">
-        <v>525.5</v>
+        <v>-96.7</v>
       </c>
       <c r="L3">
-        <v>0.1720581494335669</v>
+        <v>-0.03977132516245784</v>
       </c>
       <c r="M3">
-        <v>919.4000000000001</v>
+        <v>353.9</v>
       </c>
       <c r="N3">
-        <v>0.3086581394568101</v>
+        <v>0.1163379355687048</v>
       </c>
       <c r="O3">
-        <v>1.749571836346337</v>
+        <v>-3.659772492244053</v>
       </c>
       <c r="P3">
-        <v>187.3</v>
+        <v>172.3</v>
       </c>
       <c r="Q3">
-        <v>0.0628797797696982</v>
+        <v>0.05664036817882972</v>
       </c>
       <c r="R3">
-        <v>0.3564224548049477</v>
+        <v>-1.781799379524302</v>
       </c>
       <c r="S3">
-        <v>732.1000000000001</v>
+        <v>181.6</v>
       </c>
       <c r="T3">
-        <v>0.796280182727866</v>
+        <v>0.5131393048883864</v>
       </c>
       <c r="U3">
-        <v>1000.1</v>
+        <v>653.4</v>
       </c>
       <c r="V3">
-        <v>0.3357504951824622</v>
+        <v>0.214792899408284</v>
       </c>
       <c r="W3">
-        <v>0.5986557302346777</v>
+        <v>-0.1724937566892615</v>
       </c>
       <c r="X3">
-        <v>0.1007241411887352</v>
+        <v>0.07998372902819928</v>
       </c>
       <c r="Y3">
-        <v>0.4979315890459424</v>
+        <v>-0.2524774857174608</v>
       </c>
       <c r="Z3">
-        <v>1.631468419752576</v>
+        <v>1.471530886588896</v>
       </c>
       <c r="AA3">
-        <v>-0.008240536917160613</v>
+        <v>-0.009065326930548285</v>
       </c>
       <c r="AB3">
-        <v>0.08106367527907257</v>
+        <v>0.06837693492362432</v>
       </c>
       <c r="AC3">
-        <v>-0.08930421219623319</v>
+        <v>-0.07744226185417261</v>
       </c>
       <c r="AD3">
-        <v>1998.2</v>
+        <v>2032.1</v>
       </c>
       <c r="AE3">
-        <v>503.4558504363756</v>
+        <v>469.392875507454</v>
       </c>
       <c r="AF3">
-        <v>2501.655850436376</v>
+        <v>2501.492875507454</v>
       </c>
       <c r="AG3">
-        <v>1501.555850436376</v>
+        <v>1848.092875507454</v>
       </c>
       <c r="AH3">
-        <v>0.4564769001701195</v>
+        <v>0.4512485055333396</v>
       </c>
       <c r="AI3">
-        <v>0.6657844962159285</v>
+        <v>0.833055418477612</v>
       </c>
       <c r="AJ3">
-        <v>0.3351495763997774</v>
+        <v>0.3779259254489464</v>
       </c>
       <c r="AK3">
-        <v>0.5445636805270315</v>
+        <v>0.7866257256391302</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>24.79156327543425</v>
+        <v>25.7553865652725</v>
       </c>
       <c r="AP3">
-        <v>18.62972519151831</v>
+        <v>23.4232303613112</v>
       </c>
     </row>
   </sheetData>
